--- a/projects/NZIPL/docs/trade_data/latest_2024/NZIPL_2024_CountryTotals_Imports_USDmn.xlsx
+++ b/projects/NZIPL/docs/trade_data/latest_2024/NZIPL_2024_CountryTotals_Imports_USDmn.xlsx
@@ -94,7 +94,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-10</t>
+    <t xml:space="preserve">2026-07-11</t>
   </si>
   <si>
     <t xml:space="preserve">ISO3</t>
@@ -1560,7 +1560,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>136060.673</v>
+        <v>136064.651</v>
       </c>
     </row>
     <row r="3">
@@ -1571,7 +1571,7 @@
         <v>34</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>92158.16</v>
+        <v>92345.318</v>
       </c>
     </row>
     <row r="4">
@@ -1582,7 +1582,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>54258.639</v>
+        <v>54352.435</v>
       </c>
     </row>
     <row r="5">
@@ -1593,7 +1593,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>31957.155</v>
+        <v>32146.707</v>
       </c>
     </row>
     <row r="6">
@@ -1604,7 +1604,7 @@
         <v>44</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>16765.002</v>
+        <v>16830.796</v>
       </c>
     </row>
     <row r="7">
@@ -1615,7 +1615,7 @@
         <v>46</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>22361.852</v>
+        <v>22495.159</v>
       </c>
     </row>
     <row r="8">
@@ -1626,7 +1626,7 @@
         <v>38</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>22692.008</v>
+        <v>22730.806</v>
       </c>
     </row>
     <row r="9">
@@ -1637,7 +1637,7 @@
         <v>42</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>20091.311</v>
+        <v>20153.044</v>
       </c>
     </row>
     <row r="10">
@@ -1648,7 +1648,7 @@
         <v>60</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>28414.106</v>
+        <v>28421.891</v>
       </c>
     </row>
     <row r="11">
@@ -1659,7 +1659,7 @@
         <v>48</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>17876.961</v>
+        <v>18196.377</v>
       </c>
     </row>
     <row r="12">
@@ -1670,7 +1670,7 @@
         <v>50</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>18511.918</v>
+        <v>18520.24</v>
       </c>
     </row>
     <row r="13">
@@ -1681,7 +1681,7 @@
         <v>64</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>15297.44</v>
+        <v>15441.807</v>
       </c>
     </row>
     <row r="14">
@@ -1692,7 +1692,7 @@
         <v>58</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>11007.791</v>
+        <v>11022.674</v>
       </c>
     </row>
     <row r="15">
@@ -1703,7 +1703,7 @@
         <v>30</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>8078.789</v>
+        <v>8144.785</v>
       </c>
     </row>
     <row r="16">
@@ -1714,7 +1714,7 @@
         <v>54</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>22181.133</v>
+        <v>22186.591</v>
       </c>
     </row>
     <row r="17">
@@ -1725,7 +1725,7 @@
         <v>56</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>8490.71</v>
+        <v>8671.063</v>
       </c>
     </row>
     <row r="18">
@@ -1736,7 +1736,7 @@
         <v>52</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3008.548</v>
+        <v>3179.551</v>
       </c>
     </row>
     <row r="19">
@@ -1747,7 +1747,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>8429.194</v>
+        <v>8429.295</v>
       </c>
     </row>
     <row r="20">
@@ -1758,7 +1758,7 @@
         <v>74</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>14508.723</v>
+        <v>14555.184</v>
       </c>
     </row>
     <row r="21">
@@ -1769,7 +1769,7 @@
         <v>40</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>10399.925</v>
+        <v>10598.037</v>
       </c>
     </row>
     <row r="22">
@@ -1780,7 +1780,7 @@
         <v>88</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>12574.182</v>
+        <v>12575.236</v>
       </c>
     </row>
     <row r="23">
@@ -1791,29 +1791,29 @@
         <v>84</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>8456.904</v>
+        <v>8467.652</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>10479.501</v>
+        <v>8114.216</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>8047.965</v>
+        <v>10479.501</v>
       </c>
     </row>
     <row r="26">
@@ -1824,7 +1824,7 @@
         <v>86</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>14298.208</v>
+        <v>14558.789</v>
       </c>
     </row>
     <row r="27">
@@ -1835,7 +1835,7 @@
         <v>92</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>8683.817</v>
+        <v>8684.93</v>
       </c>
     </row>
     <row r="28">
@@ -1857,7 +1857,7 @@
         <v>70</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>10179.617</v>
+        <v>10179.807</v>
       </c>
     </row>
     <row r="30">
@@ -1868,7 +1868,7 @@
         <v>80</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>5925.337</v>
+        <v>5925.411</v>
       </c>
     </row>
     <row r="31">
@@ -1879,7 +1879,7 @@
         <v>78</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>5959.005</v>
+        <v>5959.208</v>
       </c>
     </row>
   </sheetData>
@@ -1917,7 +1917,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>232500.98</v>
+        <v>232507.138</v>
       </c>
     </row>
     <row r="3">
@@ -1928,7 +1928,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>4168.098</v>
+        <v>4174.732</v>
       </c>
     </row>
     <row r="4">
@@ -1939,7 +1939,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>33639.717</v>
+        <v>33673.387</v>
       </c>
     </row>
     <row r="5">
@@ -1950,7 +1950,7 @@
         <v>34</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>44592.957</v>
+        <v>44636.765</v>
       </c>
     </row>
     <row r="6">
@@ -1961,7 +1961,7 @@
         <v>36</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>32467.244</v>
+        <v>32470.171</v>
       </c>
     </row>
     <row r="7">
@@ -1972,7 +1972,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>24706.688</v>
+        <v>24715.927</v>
       </c>
     </row>
     <row r="8">
@@ -1983,7 +1983,7 @@
         <v>40</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4044.395</v>
+        <v>4049.524</v>
       </c>
     </row>
     <row r="9">
@@ -1994,7 +1994,7 @@
         <v>42</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>10268.607</v>
+        <v>10292.584</v>
       </c>
     </row>
     <row r="10">
@@ -2005,7 +2005,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7344.443</v>
+        <v>7361.919</v>
       </c>
     </row>
     <row r="11">
@@ -2016,7 +2016,7 @@
         <v>46</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>10936.758</v>
+        <v>10951.378</v>
       </c>
     </row>
     <row r="12">
@@ -2027,7 +2027,7 @@
         <v>48</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>8544.118</v>
+        <v>8551.068</v>
       </c>
     </row>
     <row r="13">
@@ -2038,7 +2038,7 @@
         <v>50</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>11077.189</v>
+        <v>11089.578</v>
       </c>
     </row>
     <row r="14">
@@ -2049,7 +2049,7 @@
         <v>52</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1003.186</v>
+        <v>1247.52</v>
       </c>
     </row>
     <row r="15">
@@ -2060,7 +2060,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>17026.603</v>
+        <v>17031.696</v>
       </c>
     </row>
     <row r="16">
@@ -2071,7 +2071,7 @@
         <v>56</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>8733.484</v>
+        <v>8747.061</v>
       </c>
     </row>
     <row r="17">
@@ -2082,7 +2082,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>7644.561</v>
+        <v>7650.724</v>
       </c>
     </row>
     <row r="18">
@@ -2093,7 +2093,7 @@
         <v>60</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>15503.567</v>
+        <v>15511.758</v>
       </c>
     </row>
     <row r="19">
@@ -2104,7 +2104,7 @@
         <v>62</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>7993.483</v>
+        <v>7997.102</v>
       </c>
     </row>
     <row r="20">
@@ -2115,7 +2115,7 @@
         <v>64</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>8504.975</v>
+        <v>8521.82</v>
       </c>
     </row>
     <row r="21">
@@ -2126,7 +2126,7 @@
         <v>66</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5658.838</v>
+        <v>5659.233</v>
       </c>
     </row>
     <row r="22">
@@ -2137,7 +2137,7 @@
         <v>68</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2930.825</v>
+        <v>2938.833</v>
       </c>
     </row>
     <row r="23">
@@ -2148,7 +2148,7 @@
         <v>70</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7262.322</v>
+        <v>7277.977</v>
       </c>
     </row>
     <row r="24">
@@ -2159,7 +2159,7 @@
         <v>72</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>777.36</v>
+        <v>779.593</v>
       </c>
     </row>
     <row r="25">
@@ -2170,7 +2170,7 @@
         <v>74</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>7615.573</v>
+        <v>7636.178</v>
       </c>
     </row>
     <row r="26">
@@ -2181,7 +2181,7 @@
         <v>76</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>4203.859</v>
+        <v>4208.772</v>
       </c>
     </row>
     <row r="27">
@@ -2192,7 +2192,7 @@
         <v>78</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>2952.649</v>
+        <v>2957.922</v>
       </c>
     </row>
     <row r="28">
@@ -2203,7 +2203,7 @@
         <v>80</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3518.535</v>
+        <v>3524.099</v>
       </c>
     </row>
     <row r="29">
@@ -2214,7 +2214,7 @@
         <v>82</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>3957.527</v>
+        <v>3964.137</v>
       </c>
     </row>
     <row r="30">
@@ -2225,7 +2225,7 @@
         <v>84</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>3729.753</v>
+        <v>3733.593</v>
       </c>
     </row>
     <row r="31">
@@ -2236,7 +2236,7 @@
         <v>86</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>7209.962</v>
+        <v>7211.823</v>
       </c>
     </row>
   </sheetData>
@@ -2274,7 +2274,7 @@
         <v>34</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>23033.848</v>
+        <v>23925.656</v>
       </c>
     </row>
     <row r="3">
@@ -2285,7 +2285,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>17049.53</v>
+        <v>18138.906</v>
       </c>
     </row>
     <row r="4">
@@ -2296,7 +2296,7 @@
         <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>35999.086</v>
+        <v>36011.327</v>
       </c>
     </row>
     <row r="5">
@@ -2307,7 +2307,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10860.298</v>
+        <v>10860.57</v>
       </c>
     </row>
     <row r="6">
@@ -2318,7 +2318,7 @@
         <v>48</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7437.179</v>
+        <v>7891.138</v>
       </c>
     </row>
     <row r="7">
@@ -2329,7 +2329,7 @@
         <v>50</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8104.551</v>
+        <v>10763.948</v>
       </c>
     </row>
     <row r="8">
@@ -2340,7 +2340,7 @@
         <v>44</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5217.551</v>
+        <v>5694.882</v>
       </c>
     </row>
     <row r="9">
@@ -2351,7 +2351,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>7315.553</v>
+        <v>7325.66</v>
       </c>
     </row>
     <row r="10">
@@ -2362,29 +2362,29 @@
         <v>46</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5955.262</v>
+        <v>7197.282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1706.84</v>
+        <v>8208.445</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6798.884</v>
+        <v>1706.84</v>
       </c>
     </row>
     <row r="13">
@@ -2395,7 +2395,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>10004.196</v>
+        <v>10395.425</v>
       </c>
     </row>
     <row r="14">
@@ -2428,7 +2428,7 @@
         <v>64</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>3535.73</v>
+        <v>3910.934</v>
       </c>
     </row>
     <row r="17">
@@ -2439,7 +2439,7 @@
         <v>78</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3676.275</v>
+        <v>3796.091</v>
       </c>
     </row>
     <row r="18">
@@ -2450,7 +2450,7 @@
         <v>60</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>5494.334</v>
+        <v>5494.456</v>
       </c>
     </row>
     <row r="19">
@@ -2461,7 +2461,7 @@
         <v>40</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4318.406</v>
+        <v>4318.599</v>
       </c>
     </row>
     <row r="20">
@@ -2494,7 +2494,7 @@
         <v>70</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>3201.738</v>
+        <v>3264.4</v>
       </c>
     </row>
     <row r="23">
@@ -2505,29 +2505,29 @@
         <v>56</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>3165.798</v>
+        <v>3166.107</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2660.385</v>
+        <v>3907.269</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>3660.639</v>
+        <v>2661.558</v>
       </c>
     </row>
     <row r="26">
@@ -2549,7 +2549,7 @@
         <v>92</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>2570.775</v>
+        <v>2653.974</v>
       </c>
     </row>
     <row r="28">
@@ -2560,7 +2560,7 @@
         <v>82</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1799.258</v>
+        <v>2030.896</v>
       </c>
     </row>
     <row r="29">
@@ -2571,7 +2571,7 @@
         <v>94</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>3490.896</v>
+        <v>3491.02</v>
       </c>
     </row>
     <row r="30">
@@ -2582,7 +2582,7 @@
         <v>76</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>2517.827</v>
+        <v>2623.185</v>
       </c>
     </row>
     <row r="31">
@@ -2593,7 +2593,7 @@
         <v>80</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2796.478</v>
+        <v>2801.876</v>
       </c>
     </row>
   </sheetData>
@@ -2631,7 +2631,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>236570.502</v>
+        <v>239515.634</v>
       </c>
     </row>
     <row r="3">
@@ -2653,7 +2653,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>62129.721</v>
+        <v>62173.59</v>
       </c>
     </row>
     <row r="5">
@@ -2664,7 +2664,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>39164.462</v>
+        <v>39356.064</v>
       </c>
     </row>
     <row r="6">
@@ -2675,7 +2675,7 @@
         <v>30</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8476.526</v>
+        <v>8522.581</v>
       </c>
     </row>
     <row r="7">
@@ -2686,7 +2686,7 @@
         <v>42</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>26191.255</v>
+        <v>26211.83</v>
       </c>
     </row>
     <row r="8">
@@ -2708,7 +2708,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>29205.297</v>
+        <v>29580.037</v>
       </c>
     </row>
     <row r="10">
@@ -2752,7 +2752,7 @@
         <v>44</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>17373.373</v>
+        <v>17373.602</v>
       </c>
     </row>
     <row r="14">
@@ -2763,7 +2763,7 @@
         <v>64</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>18964.238</v>
+        <v>18984.988</v>
       </c>
     </row>
     <row r="15">
@@ -2774,7 +2774,7 @@
         <v>50</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>24913.531</v>
+        <v>24913.684</v>
       </c>
     </row>
     <row r="16">
@@ -2796,7 +2796,7 @@
         <v>58</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>21371.326</v>
+        <v>21509.325</v>
       </c>
     </row>
     <row r="18">
@@ -2851,7 +2851,7 @@
         <v>82</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>11932.243</v>
+        <v>11965.107</v>
       </c>
     </row>
     <row r="23">
@@ -2873,7 +2873,7 @@
         <v>52</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1379.98</v>
+        <v>1409.565</v>
       </c>
     </row>
     <row r="25">
@@ -2884,7 +2884,7 @@
         <v>88</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>9151.479</v>
+        <v>9151.722</v>
       </c>
     </row>
     <row r="26">
@@ -2906,7 +2906,7 @@
         <v>62</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>8010.323</v>
+        <v>8010.438</v>
       </c>
     </row>
     <row r="28">
@@ -2917,7 +2917,7 @@
         <v>70</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>11953.652</v>
+        <v>11953.998</v>
       </c>
     </row>
     <row r="29">
@@ -2939,7 +2939,7 @@
         <v>68</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>2945.062</v>
+        <v>2947.652</v>
       </c>
     </row>
     <row r="31">
@@ -2950,7 +2950,7 @@
         <v>76</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>6107.262</v>
+        <v>6108.335</v>
       </c>
     </row>
   </sheetData>
@@ -2988,7 +2988,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>25840.877</v>
+        <v>25932.989</v>
       </c>
     </row>
     <row r="3">
@@ -2999,7 +2999,7 @@
         <v>34</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>43053.362</v>
+        <v>43138.788</v>
       </c>
     </row>
     <row r="4">
@@ -3010,7 +3010,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>21791.838</v>
+        <v>21818.395</v>
       </c>
     </row>
     <row r="5">
@@ -3021,7 +3021,7 @@
         <v>36</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10377.952</v>
+        <v>10394.294</v>
       </c>
     </row>
     <row r="6">
@@ -3032,7 +3032,7 @@
         <v>38</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8229.03</v>
+        <v>8253.107</v>
       </c>
     </row>
     <row r="7">
@@ -3043,7 +3043,7 @@
         <v>44</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>7313.43</v>
+        <v>7320.759</v>
       </c>
     </row>
     <row r="8">
@@ -3054,7 +3054,7 @@
         <v>48</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>10030.598</v>
+        <v>10047.646</v>
       </c>
     </row>
     <row r="9">
@@ -3065,7 +3065,7 @@
         <v>56</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3313.662</v>
+        <v>3360.344</v>
       </c>
     </row>
     <row r="10">
@@ -3076,7 +3076,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>7653.934</v>
+        <v>7672.546</v>
       </c>
     </row>
     <row r="11">
@@ -3087,7 +3087,7 @@
         <v>60</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>11339.445</v>
+        <v>11352.207</v>
       </c>
     </row>
     <row r="12">
@@ -3098,7 +3098,7 @@
         <v>58</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5565.09</v>
+        <v>5570.086</v>
       </c>
     </row>
     <row r="13">
@@ -3109,7 +3109,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>8154.276</v>
+        <v>8166.348</v>
       </c>
     </row>
     <row r="14">
@@ -3120,7 +3120,7 @@
         <v>50</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7178.697</v>
+        <v>7238.374</v>
       </c>
     </row>
     <row r="15">
@@ -3131,7 +3131,7 @@
         <v>80</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4310.285</v>
+        <v>4319.949</v>
       </c>
     </row>
     <row r="16">
@@ -3142,7 +3142,7 @@
         <v>68</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1270.064</v>
+        <v>1271.754</v>
       </c>
     </row>
     <row r="17">
@@ -3153,7 +3153,7 @@
         <v>78</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5018.769</v>
+        <v>5024.021</v>
       </c>
     </row>
     <row r="18">
@@ -3164,7 +3164,7 @@
         <v>66</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2961.806</v>
+        <v>2978.06</v>
       </c>
     </row>
     <row r="19">
@@ -3175,7 +3175,7 @@
         <v>64</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4513.504</v>
+        <v>4519.017</v>
       </c>
     </row>
     <row r="20">
@@ -3186,7 +3186,7 @@
         <v>76</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4592.633</v>
+        <v>4599.885</v>
       </c>
     </row>
     <row r="21">
@@ -3197,7 +3197,7 @@
         <v>88</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5057.122</v>
+        <v>5107.799</v>
       </c>
     </row>
     <row r="22">
@@ -3208,7 +3208,7 @@
         <v>74</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5455.29</v>
+        <v>5468.064</v>
       </c>
     </row>
     <row r="23">
@@ -3219,7 +3219,7 @@
         <v>54</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>8695.487</v>
+        <v>8719.937</v>
       </c>
     </row>
     <row r="24">
@@ -3230,7 +3230,7 @@
         <v>70</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>3150.264</v>
+        <v>3180.581</v>
       </c>
     </row>
     <row r="25">
@@ -3241,7 +3241,7 @@
         <v>82</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>2193.744</v>
+        <v>2194.573</v>
       </c>
     </row>
     <row r="26">
@@ -3252,7 +3252,7 @@
         <v>92</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>3609.915</v>
+        <v>3612.355</v>
       </c>
     </row>
     <row r="27">
@@ -3263,7 +3263,7 @@
         <v>84</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>2708.225</v>
+        <v>2716.834</v>
       </c>
     </row>
     <row r="28">
@@ -3274,7 +3274,7 @@
         <v>40</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>4464.992</v>
+        <v>4506.567</v>
       </c>
     </row>
     <row r="29">
@@ -3285,7 +3285,7 @@
         <v>86</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>4345.312</v>
+        <v>4360.907</v>
       </c>
     </row>
     <row r="30">
@@ -3296,7 +3296,7 @@
         <v>62</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>4614.152</v>
+        <v>4655.044</v>
       </c>
     </row>
     <row r="31">
@@ -3307,7 +3307,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>3236.298</v>
+        <v>3254.409</v>
       </c>
     </row>
   </sheetData>
@@ -4059,7 +4059,7 @@
         <v>28</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>91327.929</v>
+        <v>91392.697</v>
       </c>
     </row>
     <row r="3">
@@ -4070,7 +4070,7 @@
         <v>36</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>18368.714</v>
+        <v>18653.015</v>
       </c>
     </row>
     <row r="4">
@@ -4081,7 +4081,7 @@
         <v>34</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>16166.098</v>
+        <v>16411.661</v>
       </c>
     </row>
     <row r="5">
@@ -4092,7 +4092,7 @@
         <v>32</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11242.007</v>
+        <v>11551.327</v>
       </c>
     </row>
     <row r="6">
@@ -4103,7 +4103,7 @@
         <v>52</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>240.517</v>
+        <v>241.699</v>
       </c>
     </row>
     <row r="7">
@@ -4114,7 +4114,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>8221.827</v>
+        <v>8375.002</v>
       </c>
     </row>
     <row r="8">
@@ -4125,7 +4125,7 @@
         <v>42</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3432.819</v>
+        <v>3452.387</v>
       </c>
     </row>
     <row r="9">
@@ -4136,7 +4136,7 @@
         <v>72</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>154.38</v>
+        <v>154.878</v>
       </c>
     </row>
     <row r="10">
@@ -4147,7 +4147,7 @@
         <v>30</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1135.496</v>
+        <v>1143.046</v>
       </c>
     </row>
     <row r="11">
@@ -4158,7 +4158,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3025.393</v>
+        <v>3071.483</v>
       </c>
     </row>
     <row r="12">
@@ -4169,7 +4169,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2175.914</v>
+        <v>2186.319</v>
       </c>
     </row>
     <row r="13">
@@ -4180,7 +4180,7 @@
         <v>40</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1678.422</v>
+        <v>1689.14</v>
       </c>
     </row>
     <row r="14">
@@ -4191,7 +4191,7 @@
         <v>64</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5428.492</v>
+        <v>5447.534</v>
       </c>
     </row>
     <row r="15">
@@ -4202,7 +4202,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>7675.746</v>
+        <v>7772.891</v>
       </c>
     </row>
     <row r="16">
@@ -4213,7 +4213,7 @@
         <v>60</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>7258.311</v>
+        <v>7380.675</v>
       </c>
     </row>
     <row r="17">
@@ -4224,7 +4224,7 @@
         <v>50</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>3472.156</v>
+        <v>3513.452</v>
       </c>
     </row>
     <row r="18">
@@ -4235,7 +4235,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>3062.91</v>
+        <v>3098.386</v>
       </c>
     </row>
     <row r="19">
@@ -4246,7 +4246,7 @@
         <v>46</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>3262.968</v>
+        <v>3334.423</v>
       </c>
     </row>
     <row r="20">
@@ -4257,7 +4257,7 @@
         <v>98</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>711.875</v>
+        <v>714.319</v>
       </c>
     </row>
     <row r="21">
@@ -4268,7 +4268,7 @@
         <v>66</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1253.173</v>
+        <v>1274.108</v>
       </c>
     </row>
     <row r="22">
@@ -4279,29 +4279,29 @@
         <v>48</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2432.138</v>
+        <v>2453.747</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>706.764</v>
+        <v>2570.436</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2421.445</v>
+        <v>711.533</v>
       </c>
     </row>
     <row r="25">
@@ -4312,7 +4312,7 @@
         <v>70</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>2846.308</v>
+        <v>2905.815</v>
       </c>
     </row>
     <row r="26">
@@ -4323,7 +4323,7 @@
         <v>78</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>1427.791</v>
+        <v>1464.261</v>
       </c>
     </row>
     <row r="27">
@@ -4334,29 +4334,29 @@
         <v>74</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>3557.625</v>
+        <v>3625.826</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1583.658</v>
+        <v>2264.436</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2177.466</v>
+        <v>1593.924</v>
       </c>
     </row>
     <row r="30">
@@ -4367,7 +4367,7 @@
         <v>84</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1788.282</v>
+        <v>1801.643</v>
       </c>
     </row>
     <row r="31">
@@ -4378,7 +4378,7 @@
         <v>82</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2127.223</v>
+        <v>2134.295</v>
       </c>
     </row>
   </sheetData>
@@ -4427,7 +4427,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>687.16</v>
+        <v>687.236</v>
       </c>
     </row>
     <row r="4">
@@ -4460,7 +4460,7 @@
         <v>34</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>13427.926</v>
+        <v>13428.737</v>
       </c>
     </row>
     <row r="7">
@@ -4526,7 +4526,7 @@
         <v>54</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6930.698</v>
+        <v>6930.756</v>
       </c>
     </row>
     <row r="13">
@@ -4592,7 +4592,7 @@
         <v>64</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>4315.459</v>
+        <v>4315.602</v>
       </c>
     </row>
     <row r="19">
@@ -4702,7 +4702,7 @@
         <v>70</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3432.511</v>
+        <v>3432.633</v>
       </c>
     </row>
     <row r="29">
@@ -4713,7 +4713,7 @@
         <v>86</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2015.006</v>
+        <v>2083.427</v>
       </c>
     </row>
     <row r="30">
